--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MASSACHUSETTS_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MASSACHUSETTS_2019.xlsx
@@ -733,7 +733,7 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="22">
@@ -1147,7 +1147,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="45">
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="D65">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="66">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C69">
@@ -2677,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="D129">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="130">
@@ -3181,7 +3181,7 @@
         <v>5</v>
       </c>
       <c r="D157">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="158">
@@ -3217,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="D159">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="160">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C170">
@@ -5053,7 +5053,7 @@
         <v>5</v>
       </c>
       <c r="D261">
-        <v>0.009633911368015413</v>
+        <v>0.009633911368015412</v>
       </c>
     </row>
     <row r="262">
